--- a/src/resources/Docs/_IV/Wissen_MorganStanley_SystemDesign.xlsx
+++ b/src/resources/Docs/_IV/Wissen_MorganStanley_SystemDesign.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Prac\GIT_Repo\CoreJava\src\resources\Docs\_IV\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D03B1D9-1433-47B3-8C4B-D43A1FFA3997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7665" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -109,19 +110,19 @@
     <t>replicas</t>
   </si>
   <si>
-    <t>username, bookname, qty, borrwostDate, borrowEndDate</t>
-  </si>
-  <si>
-    <t>username, bookname, qty, borrwostDate, borrowEndDate, isValid</t>
-  </si>
-  <si>
     <t>resonpse</t>
+  </si>
+  <si>
+    <t>username, bookname, qty, borrowStartDate, borrowEndDate</t>
+  </si>
+  <si>
+    <t>username, bookname, qty, borrowStartDate, borrowEndDate, isValid</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -138,7 +139,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -146,17 +147,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -437,7 +469,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:E8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -505,7 +537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:S22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -513,209 +545,209 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="E3" s="2" t="s">
+      <c r="C3" s="2"/>
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="O3" s="1" t="s">
+      <c r="F3" s="1"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="O3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="1"/>
+      <c r="P3" s="2"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="1" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="R6" s="1" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="R6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S6" s="1"/>
+      <c r="S6" s="2"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="N12" s="1" t="s">
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="N12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="O12" s="1"/>
+      <c r="O12" s="2"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>23</v>
       </c>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="R14" s="1" t="s">
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="R14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="S14" s="1"/>
+      <c r="S14" s="2"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>24</v>
       </c>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>25</v>
       </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
         <v>28</v>
       </c>
-      <c r="B21" t="s">
-        <v>27</v>
-      </c>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -734,7 +766,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
@@ -743,7 +775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
@@ -752,7 +784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
